--- a/data/trans_orig/dukeGLOBAL-Edad-trans_orig.xlsx
+++ b/data/trans_orig/dukeGLOBAL-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media de la escala global de apoyo funcional social (Duke)</t>
+          <t>Puntuación media de la escala global de apoyo funcional social (Duke) (tasa de respuesta: 98,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>48,83; 49,96</t>
+          <t>48,75; 49,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,4; 50,5</t>
+          <t>49,36; 50,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,95; 49,08</t>
+          <t>47,9; 49,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50,93; 52,48</t>
+          <t>50,88; 52,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>48,07; 49,36</t>
+          <t>48,01; 49,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,09; 50,21</t>
+          <t>49,11; 50,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,15; 49,25</t>
+          <t>48,11; 49,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>48,94; 51,34</t>
+          <t>48,91; 51,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>48,65; 49,5</t>
+          <t>48,67; 49,49</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49,4; 50,22</t>
+          <t>49,42; 50,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48,23; 49,04</t>
+          <t>48,23; 49,06</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50,28; 51,71</t>
+          <t>50,31; 51,68</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>48,5; 49,54</t>
+          <t>48,52; 49,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,92; 49,91</t>
+          <t>48,87; 49,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47,24; 48,29</t>
+          <t>47,28; 48,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48,62; 50,26</t>
+          <t>48,64; 50,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,43; 48,74</t>
+          <t>47,43; 48,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,87; 49,03</t>
+          <t>47,93; 49,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,66; 48,6</t>
+          <t>47,69; 48,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>49,54; 52,07</t>
+          <t>49,55; 52,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>48,22; 49,03</t>
+          <t>48,15; 49,01</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48,55; 49,32</t>
+          <t>48,58; 49,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47,6; 48,31</t>
+          <t>47,63; 48,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>49,43; 51,2</t>
+          <t>49,42; 51,08</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46,78; 48,04</t>
+          <t>46,78; 48,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47,6; 48,72</t>
+          <t>47,59; 48,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46,95; 47,94</t>
+          <t>46,97; 47,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47,99; 49,36</t>
+          <t>48,01; 49,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46,92; 48,14</t>
+          <t>46,85; 48,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,46; 48,54</t>
+          <t>47,5; 48,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,02; 48,02</t>
+          <t>47,07; 48,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,7; 49,64</t>
+          <t>48,66; 49,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47,03; 47,93</t>
+          <t>47,02; 47,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47,69; 48,51</t>
+          <t>47,75; 48,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47,15; 47,86</t>
+          <t>47,12; 47,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48,51; 49,33</t>
+          <t>48,58; 49,33</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>46,57; 47,99</t>
+          <t>46,53; 47,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47,39; 48,63</t>
+          <t>47,45; 48,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45,2; 46,49</t>
+          <t>45,2; 46,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47,82; 52,78</t>
+          <t>47,8; 52,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,45; 47,0</t>
+          <t>45,44; 46,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,24; 47,56</t>
+          <t>46,24; 47,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,65; 46,78</t>
+          <t>45,67; 46,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>47,89; 49,39</t>
+          <t>47,91; 49,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46,24; 47,28</t>
+          <t>46,21; 47,32</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47,08; 47,97</t>
+          <t>47,08; 47,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45,59; 46,43</t>
+          <t>45,59; 46,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,09; 51,57</t>
+          <t>48,12; 51,38</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>45,78; 47,46</t>
+          <t>45,8; 47,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>47,77; 49,21</t>
+          <t>47,84; 49,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,46; 46,85</t>
+          <t>45,46; 46,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46,09; 47,53</t>
+          <t>46,21; 47,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>44,18; 45,86</t>
+          <t>44,11; 45,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,0; 47,52</t>
+          <t>45,89; 47,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,37; 45,84</t>
+          <t>44,39; 45,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>45,82; 46,91</t>
+          <t>45,77; 46,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>45,2; 46,4</t>
+          <t>45,17; 46,46</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47,06; 48,13</t>
+          <t>47,07; 48,1</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45,16; 46,15</t>
+          <t>45,11; 46,14</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>46,17; 47,06</t>
+          <t>46,2; 47,05</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44,67; 46,58</t>
+          <t>44,66; 46,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46,13; 47,98</t>
+          <t>46,28; 48,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45,85; 47,42</t>
+          <t>45,95; 47,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46,09; 47,55</t>
+          <t>46,09; 47,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43,77; 45,67</t>
+          <t>43,79; 45,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45,54; 47,17</t>
+          <t>45,4; 47,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,79; 45,35</t>
+          <t>43,8; 45,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>46,41; 47,62</t>
+          <t>46,44; 47,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44,49; 45,89</t>
+          <t>44,54; 45,86</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>46,18; 47,39</t>
+          <t>46,1; 47,35</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>45,06; 46,14</t>
+          <t>45,01; 46,12</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>46,48; 47,46</t>
+          <t>46,46; 47,46</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>42,67; 45,18</t>
+          <t>42,56; 45,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>44,27; 46,57</t>
+          <t>44,35; 46,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43,84; 45,58</t>
+          <t>43,87; 45,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44,83; 46,55</t>
+          <t>44,88; 46,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>41,16; 43,72</t>
+          <t>41,23; 43,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,31; 47,03</t>
+          <t>45,36; 46,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,74; 44,81</t>
+          <t>42,78; 44,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>43,14; 44,57</t>
+          <t>43,17; 44,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>42,18; 43,91</t>
+          <t>42,0; 43,92</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45,22; 46,64</t>
+          <t>45,23; 46,6</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43,53; 44,9</t>
+          <t>43,53; 44,96</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>44,08; 45,18</t>
+          <t>44,07; 45,17</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>47,33; 47,87</t>
+          <t>47,33; 47,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>48,13; 48,63</t>
+          <t>48,11; 48,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46,64; 47,13</t>
+          <t>46,65; 47,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48,17; 50,27</t>
+          <t>48,18; 50,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>46,21; 46,8</t>
+          <t>46,24; 46,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,36; 47,86</t>
+          <t>47,33; 47,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,24; 46,73</t>
+          <t>46,18; 46,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>47,69; 48,47</t>
+          <t>47,73; 48,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>46,84; 47,26</t>
+          <t>46,86; 47,25</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47,83; 48,18</t>
+          <t>47,8; 48,16</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46,49; 46,84</t>
+          <t>46,5; 46,85</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>48,03; 49,33</t>
+          <t>48,03; 49,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/dukeGLOBAL-Edad-trans_orig.xlsx
+++ b/data/trans_orig/dukeGLOBAL-Edad-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51,77</t>
+          <t>51,25</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>50,27</t>
+          <t>49,97</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>51,12</t>
+          <t>50,65</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>48,75; 49,97</t>
+          <t>48,86; 49,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,36; 50,51</t>
+          <t>49,38; 50,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,9; 49,09</t>
+          <t>47,96; 49,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50,88; 52,53</t>
+          <t>50,07; 52,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>48,01; 49,38</t>
+          <t>48,09; 49,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,11; 50,19</t>
+          <t>49,07; 50,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,11; 49,32</t>
+          <t>48,22; 49,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>48,91; 51,26</t>
+          <t>48,69; 51,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>48,67; 49,49</t>
+          <t>48,63; 49,48</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49,42; 50,2</t>
+          <t>49,45; 50,22</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48,23; 49,06</t>
+          <t>48,27; 49,01</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50,31; 51,68</t>
+          <t>49,87; 51,31</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49,47</t>
+          <t>49,04</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>50,52</t>
+          <t>49,37</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>50,04</t>
+          <t>49,21</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>48,52; 49,56</t>
+          <t>48,5; 49,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,87; 49,83</t>
+          <t>48,9; 49,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47,28; 48,26</t>
+          <t>47,27; 48,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48,64; 50,13</t>
+          <t>48,15; 49,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,43; 48,7</t>
+          <t>47,45; 48,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,93; 49,06</t>
+          <t>47,92; 49,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,69; 48,61</t>
+          <t>47,69; 48,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>49,55; 52,21</t>
+          <t>48,67; 50,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>48,15; 49,01</t>
+          <t>48,21; 49,01</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48,58; 49,33</t>
+          <t>48,58; 49,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47,63; 48,3</t>
+          <t>47,58; 48,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>49,42; 51,08</t>
+          <t>48,57; 49,7</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48,69</t>
+          <t>48,47</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>49,21</t>
+          <t>48,97</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>48,95</t>
+          <t>48,72</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46,78; 48,13</t>
+          <t>46,73; 48,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47,59; 48,73</t>
+          <t>47,54; 48,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46,97; 47,99</t>
+          <t>46,91; 47,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48,01; 49,39</t>
+          <t>47,71; 49,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46,85; 48,04</t>
+          <t>46,91; 48,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,5; 48,58</t>
+          <t>47,48; 48,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,07; 48,08</t>
+          <t>47,11; 48,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,66; 49,65</t>
+          <t>48,47; 49,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47,02; 47,91</t>
+          <t>47,01; 47,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47,75; 48,53</t>
+          <t>47,69; 48,5</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47,12; 47,87</t>
+          <t>47,17; 47,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48,58; 49,33</t>
+          <t>48,31; 49,12</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49,98</t>
+          <t>47,9</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>48,46</t>
+          <t>47,94</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>49,31</t>
+          <t>47,92</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>46,53; 47,97</t>
+          <t>46,6; 47,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47,45; 48,62</t>
+          <t>47,41; 48,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45,2; 46,43</t>
+          <t>45,17; 46,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47,8; 52,88</t>
+          <t>47,19; 48,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,44; 46,93</t>
+          <t>45,51; 46,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,24; 47,57</t>
+          <t>46,29; 47,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,67; 46,77</t>
+          <t>45,64; 46,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>47,91; 49,47</t>
+          <t>47,48; 48,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46,21; 47,32</t>
+          <t>46,22; 47,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47,08; 47,99</t>
+          <t>47,05; 47,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45,59; 46,44</t>
+          <t>45,56; 46,43</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,12; 51,38</t>
+          <t>47,51; 48,31</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46,87</t>
+          <t>46,61</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>46,38</t>
+          <t>46,29</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>46,63</t>
+          <t>46,45</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>45,8; 47,46</t>
+          <t>45,81; 47,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>47,84; 49,18</t>
+          <t>47,78; 49,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,46; 46,91</t>
+          <t>45,46; 46,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46,21; 47,52</t>
+          <t>45,93; 47,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>44,11; 45,81</t>
+          <t>44,13; 45,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,89; 47,54</t>
+          <t>45,95; 47,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,39; 45,85</t>
+          <t>44,43; 45,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>45,77; 46,94</t>
+          <t>45,69; 46,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>45,17; 46,46</t>
+          <t>45,15; 46,38</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47,07; 48,1</t>
+          <t>47,03; 48,16</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45,11; 46,14</t>
+          <t>45,15; 46,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>46,2; 47,05</t>
+          <t>46,0; 46,9</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46,87</t>
+          <t>46,86</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>47,05</t>
+          <t>46,97</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46,96</t>
+          <t>46,92</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44,66; 46,6</t>
+          <t>44,7; 46,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46,28; 48,06</t>
+          <t>46,23; 47,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45,95; 47,44</t>
+          <t>45,97; 47,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46,09; 47,62</t>
+          <t>46,11; 47,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43,79; 45,76</t>
+          <t>43,78; 45,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45,4; 47,23</t>
+          <t>45,57; 47,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,8; 45,35</t>
+          <t>43,72; 45,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>46,44; 47,66</t>
+          <t>46,35; 47,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44,54; 45,86</t>
+          <t>44,48; 45,88</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>46,1; 47,35</t>
+          <t>46,11; 47,33</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>45,01; 46,12</t>
+          <t>45,02; 46,12</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>46,46; 47,46</t>
+          <t>46,43; 47,42</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45,76</t>
+          <t>45,67</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>43,89</t>
+          <t>43,88</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>44,63</t>
+          <t>44,59</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>42,56; 45,22</t>
+          <t>42,58; 45,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>44,35; 46,6</t>
+          <t>44,34; 46,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43,87; 45,6</t>
+          <t>43,8; 45,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44,88; 46,56</t>
+          <t>44,63; 46,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>41,23; 43,62</t>
+          <t>41,18; 43,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,36; 46,99</t>
+          <t>45,34; 46,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,78; 44,78</t>
+          <t>42,78; 44,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>43,17; 44,52</t>
+          <t>43,16; 44,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>42,0; 43,92</t>
+          <t>42,01; 43,93</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45,23; 46,6</t>
+          <t>45,22; 46,63</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43,53; 44,96</t>
+          <t>43,46; 44,84</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>44,07; 45,17</t>
+          <t>44,0; 45,09</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48,76</t>
+          <t>48,01</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,19 +1663,19 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
+          <t>47,63</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>47,06</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
           <t>48,0</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>47,06</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>48,0</t>
-        </is>
-      </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
           <t>46,68</t>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>48,38</t>
+          <t>47,81</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>47,33; 47,89</t>
+          <t>47,31; 47,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>48,11; 48,64</t>
+          <t>48,17; 48,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46,65; 47,12</t>
+          <t>46,66; 47,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48,18; 50,32</t>
+          <t>47,71; 48,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>46,24; 46,82</t>
+          <t>46,23; 46,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,33; 47,84</t>
+          <t>47,35; 47,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,18; 46,69</t>
+          <t>46,24; 46,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>47,73; 48,56</t>
+          <t>47,35; 47,86</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>46,86; 47,25</t>
+          <t>46,84; 47,25</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47,8; 48,16</t>
+          <t>47,81; 48,17</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46,5; 46,85</t>
+          <t>46,51; 46,86</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>48,03; 49,31</t>
+          <t>47,61; 47,99</t>
         </is>
       </c>
     </row>
